--- a/artfynd/A 47527-2024 artfynd.xlsx
+++ b/artfynd/A 47527-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111726545</v>
+        <v>111726546</v>
       </c>
       <c r="B2" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565035</v>
+        <v>565102</v>
       </c>
       <c r="R2" t="n">
-        <v>7032962</v>
+        <v>7032869</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111726547</v>
+        <v>111726540</v>
       </c>
       <c r="B3" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565129</v>
+        <v>565148</v>
       </c>
       <c r="R3" t="n">
-        <v>7032868</v>
+        <v>7032889</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111726548</v>
+        <v>111726549</v>
       </c>
       <c r="B4" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,7 +915,7 @@
         <v>564962</v>
       </c>
       <c r="R4" t="n">
-        <v>7033026</v>
+        <v>7033006</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111726549</v>
+        <v>122246481</v>
       </c>
       <c r="B5" t="n">
-        <v>98508</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,6 +1041,11 @@
           <t>Ramsele</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Y-Sol-0392</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>2023-08-20</t>
@@ -1083,7 +1068,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1093,43 +1078,38 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111726546</v>
+        <v>111726545</v>
       </c>
       <c r="B6" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565102</v>
+        <v>565035</v>
       </c>
       <c r="R6" t="n">
-        <v>7032869</v>
+        <v>7032961</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,6 +1178,410 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111726541</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>565112</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7032932</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111726547</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>565129</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7032868</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111726548</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>564962</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7033026</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111726543</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>564987</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7032945</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 47527-2024 artfynd.xlsx
+++ b/artfynd/A 47527-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726546</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726540</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726549</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122246481</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726545</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726541</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726547</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726548</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1586,8 +1631,24 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111726543</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>